--- a/base_datas/mediana_porte_detalhamento.xlsx
+++ b/base_datas/mediana_porte_detalhamento.xlsx
@@ -592,7 +592,7 @@
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>populacao_24</t>
+          <t>populacao_25</t>
         </is>
       </c>
     </row>
@@ -603,133 +603,133 @@
         </is>
       </c>
       <c r="B2">
-        <v>395.9212935291775</v>
+        <v>450.6256326690304</v>
       </c>
       <c r="C2">
-        <v>90.60633427287272</v>
+        <v>93.85868977928376</v>
       </c>
       <c r="D2">
-        <v>5563.086162420382</v>
+        <v>6160.006504565668</v>
       </c>
       <c r="E2">
-        <v>162.8730283490829</v>
+        <v>203.6991251476329</v>
       </c>
       <c r="F2">
-        <v>367.6141952724325</v>
+        <v>417.6053922671344</v>
       </c>
       <c r="G2">
-        <v>23.41674957301452</v>
+        <v>26.74412764194565</v>
       </c>
       <c r="H2">
-        <v>2.775689465983906</v>
+        <v>2.464289194246486</v>
       </c>
       <c r="I2">
-        <v>181.8157958298182</v>
+        <v>193.6979540567158</v>
       </c>
       <c r="J2">
-        <v>52.42899288848805</v>
+        <v>54.05462622262287</v>
       </c>
       <c r="K2">
-        <v>6.708029476546992E-15</v>
+        <v>6.542456719352234E-15</v>
       </c>
       <c r="L2">
-        <v>3270.892228474958</v>
+        <v>3668.231330543728</v>
       </c>
       <c r="M2">
-        <v>1094.482407120743</v>
+        <v>1198.665492033857</v>
       </c>
       <c r="N2">
-        <v>950.5581563882978</v>
+        <v>1038.276592869498</v>
       </c>
       <c r="O2">
-        <v>93.60521901051308</v>
+        <v>133.3601325301205</v>
       </c>
       <c r="P2">
-        <v>11.9085036063179</v>
+        <v>10.33738650999623</v>
       </c>
       <c r="Q2">
-        <v>0.5190509005481597</v>
+        <v>0.5236530226073101</v>
       </c>
       <c r="R2">
-        <v>5.453566542879083</v>
+        <v>7.332765104418089</v>
       </c>
       <c r="S2">
-        <v>24.19251288659726</v>
+        <v>22.99870697543174</v>
       </c>
       <c r="T2">
-        <v>23.37024884532001</v>
+        <v>26.4244898336414</v>
       </c>
       <c r="U2">
-        <v>23.36505748454561</v>
+        <v>26.703024573251</v>
       </c>
       <c r="V2">
-        <v>136.4826802753956</v>
+        <v>145.6032552932305</v>
       </c>
       <c r="W2">
-        <v>147.2139049796272</v>
+        <v>172.5681165708563</v>
       </c>
       <c r="Z2">
-        <v>1.240176007530998E-14</v>
+        <v>1.580777606904791E-14</v>
       </c>
       <c r="AA2">
-        <v>11.43544011849344</v>
+        <v>12.78764122217556</v>
       </c>
       <c r="AB2">
-        <v>13.48756383247662</v>
+        <v>14.34896476224583</v>
       </c>
       <c r="AC2">
-        <v>1.048650641961176E-16</v>
+        <v>8.818282974494701E-17</v>
       </c>
       <c r="AD2">
-        <v>0.6643962824712425</v>
+        <v>1.116777786746307</v>
       </c>
       <c r="AE2">
-        <v>2.479744236851557</v>
+        <v>8.000536172695449</v>
       </c>
       <c r="AF2">
-        <v>31.60231132377562</v>
+        <v>27.7285557212076</v>
       </c>
       <c r="AG2">
-        <v>0.236929932735426</v>
+        <v>0.2170091418460631</v>
       </c>
       <c r="AH2">
-        <v>2043.212149674385</v>
+        <v>2270.069233558672</v>
       </c>
       <c r="AJ2">
-        <v>41.06894641071767</v>
+        <v>43.97884586768421</v>
       </c>
       <c r="AK2">
-        <v>541.2672697607356</v>
+        <v>630.9461879494374</v>
       </c>
       <c r="AL2">
-        <v>116.4710996965987</v>
+        <v>116.7171192429247</v>
       </c>
       <c r="AM2">
-        <v>351.0741546905467</v>
+        <v>222.4197080774844</v>
       </c>
       <c r="AN2">
-        <v>28.43313020013492</v>
+        <v>28.53491282957244</v>
       </c>
       <c r="AO2">
-        <v>58.02238038167261</v>
+        <v>50.82110666362606</v>
       </c>
       <c r="AP2">
-        <v>759.6733585455554</v>
+        <v>835.275786531667</v>
       </c>
       <c r="AQ2">
-        <v>79.41722238000567</v>
+        <v>82.37278227755047</v>
       </c>
       <c r="AR2">
-        <v>47.34350341925303</v>
+        <v>55.19440006139949</v>
       </c>
       <c r="AS2">
-        <v>7.648910105205279</v>
+        <v>9.938647058136137</v>
       </c>
       <c r="AT2">
-        <v>3.425414449974258</v>
+        <v>3.748675733715104</v>
       </c>
       <c r="AU2">
-        <v>75.45179839391378</v>
+        <v>84.344921469453</v>
       </c>
       <c r="AV2">
         <v>1</v>
@@ -742,133 +742,133 @@
         </is>
       </c>
       <c r="B3">
-        <v>1008.7028612469</v>
+        <v>1151.697488855529</v>
       </c>
       <c r="C3">
-        <v>216.7762901087527</v>
+        <v>229.2950446271612</v>
       </c>
       <c r="D3">
-        <v>3582.600684871743</v>
+        <v>3943.36987080005</v>
       </c>
       <c r="E3">
-        <v>360.5050999086694</v>
+        <v>444.7050963348964</v>
       </c>
       <c r="F3">
-        <v>889.0500761645483</v>
+        <v>1021.207905932012</v>
       </c>
       <c r="G3">
-        <v>70.62076682310855</v>
+        <v>79.58381908443897</v>
       </c>
       <c r="H3">
-        <v>0.5724223002384561</v>
+        <v>0.5193485026561986</v>
       </c>
       <c r="I3">
-        <v>156.9513294654516</v>
+        <v>157.2140538182077</v>
       </c>
       <c r="J3">
-        <v>84.92305080587573</v>
+        <v>88.03507828112672</v>
       </c>
       <c r="K3">
-        <v>-7.674907894374933E-15</v>
+        <v>-5.392937609604782E-15</v>
       </c>
       <c r="L3">
-        <v>1637.118228708015</v>
+        <v>1828.040776081521</v>
       </c>
       <c r="M3">
-        <v>1082.87502909798</v>
+        <v>1179.783139226421</v>
       </c>
       <c r="N3">
-        <v>744.0223942308455</v>
+        <v>809.0276161597283</v>
       </c>
       <c r="O3">
-        <v>149.6290524979039</v>
+        <v>213.6648455737482</v>
       </c>
       <c r="P3">
-        <v>19.15840448869945</v>
+        <v>19.31889854378154</v>
       </c>
       <c r="Q3">
-        <v>0.1832953508763173</v>
+        <v>0.007129316731356619</v>
       </c>
       <c r="R3">
-        <v>4.261633186351126</v>
+        <v>1.907603964804308</v>
       </c>
       <c r="S3">
-        <v>79.5709891243736</v>
+        <v>98.88162806599524</v>
       </c>
       <c r="T3">
-        <v>221.7294191609912</v>
+        <v>245.0038390182517</v>
       </c>
       <c r="U3">
-        <v>69.25884397142269</v>
+        <v>87.63185848747365</v>
       </c>
       <c r="V3">
-        <v>351.4234632618296</v>
+        <v>401.3171496322813</v>
       </c>
       <c r="W3">
-        <v>198.4216890594115</v>
+        <v>224.234212003079</v>
       </c>
       <c r="Z3">
-        <v>2.483085428231813E-14</v>
+        <v>1.786744253348704E-14</v>
       </c>
       <c r="AA3">
-        <v>31.54715381938341</v>
+        <v>33.75429208975805</v>
       </c>
       <c r="AB3">
-        <v>39.63005821804789</v>
+        <v>44.29964367913524</v>
       </c>
       <c r="AC3">
-        <v>5.69262510033813E-16</v>
+        <v>-8.94031958376621E-16</v>
       </c>
       <c r="AD3">
-        <v>0.5724223002384561</v>
+        <v>0.318141573043313</v>
       </c>
       <c r="AE3">
-        <v>1.171680714203918</v>
+        <v>2.006940626276107</v>
       </c>
       <c r="AF3">
-        <v>16.29661254000684</v>
+        <v>3.955020690778755</v>
       </c>
       <c r="AG3">
-        <v>0.182543300700921</v>
+        <v>0.09331548013676666</v>
       </c>
       <c r="AH3">
-        <v>831.2152526761804</v>
+        <v>942.7559345996278</v>
       </c>
       <c r="AJ3">
-        <v>21.3555404855192</v>
+        <v>24.16460223138653</v>
       </c>
       <c r="AK3">
-        <v>467.0362849654994</v>
+        <v>475.0941768305947</v>
       </c>
       <c r="AL3">
-        <v>80.39885679264856</v>
+        <v>76.73700512961436</v>
       </c>
       <c r="AM3">
-        <v>64.23614208419022</v>
+        <v>28.63272351474025</v>
       </c>
       <c r="AN3">
-        <v>11.70409557332061</v>
+        <v>12.14586612392583</v>
       </c>
       <c r="AO3">
-        <v>21.87381012150143</v>
+        <v>19.8401654264599</v>
       </c>
       <c r="AP3">
-        <v>698.0526337624949</v>
+        <v>766.8603074847499</v>
       </c>
       <c r="AQ3">
-        <v>202.2008031127815</v>
+        <v>213.7064350395914</v>
       </c>
       <c r="AR3">
-        <v>58.3924404616661</v>
+        <v>69.17810064424573</v>
       </c>
       <c r="AS3">
-        <v>4.167602379394603</v>
+        <v>5.473453749315818</v>
       </c>
       <c r="AT3">
-        <v>2.936713520644664</v>
+        <v>2.376402405279721</v>
       </c>
       <c r="AU3">
-        <v>39.54529021152167</v>
+        <v>44.07059171268155</v>
       </c>
       <c r="AV3">
         <v>1</v>
@@ -881,133 +881,133 @@
         </is>
       </c>
       <c r="B4">
-        <v>492.2404947409619</v>
+        <v>583.6242487943942</v>
       </c>
       <c r="C4">
-        <v>117.7607563652839</v>
+        <v>124.0111320595555</v>
       </c>
       <c r="D4">
-        <v>4732.682167833893</v>
+        <v>5232.048112211221</v>
       </c>
       <c r="E4">
-        <v>185.5290676561439</v>
+        <v>231.7837004548408</v>
       </c>
       <c r="F4">
-        <v>443.9114555415077</v>
+        <v>520.2307359202779</v>
       </c>
       <c r="G4">
-        <v>33.07247701048439</v>
+        <v>38.30543527071195</v>
       </c>
       <c r="H4">
-        <v>1.246905648590856</v>
+        <v>1.05080322702753</v>
       </c>
       <c r="I4">
-        <v>176.9292844302618</v>
+        <v>187.9667100737101</v>
       </c>
       <c r="J4">
-        <v>63.3604617162261</v>
+        <v>66.01950500935814</v>
       </c>
       <c r="K4">
-        <v>7.273684587749755E-15</v>
+        <v>6.352467632158398E-15</v>
       </c>
       <c r="L4">
-        <v>2673.545560235485</v>
+        <v>3020.004460313193</v>
       </c>
       <c r="M4">
-        <v>1027.734927043608</v>
+        <v>1120.83774184834</v>
       </c>
       <c r="N4">
-        <v>911.5304557873502</v>
+        <v>977.0115791949789</v>
       </c>
       <c r="O4">
-        <v>90.86208651370625</v>
+        <v>135.3977475710441</v>
       </c>
       <c r="P4">
-        <v>12.82108592561663</v>
+        <v>11.49564814003266</v>
       </c>
       <c r="Q4">
-        <v>0.7161315062671668</v>
+        <v>0.7357870518609986</v>
       </c>
       <c r="R4">
-        <v>1.074815625777557</v>
+        <v>6.657107266695567</v>
       </c>
       <c r="S4">
-        <v>35.08755998828106</v>
+        <v>34.07317088286418</v>
       </c>
       <c r="T4">
-        <v>49.17607677666932</v>
+        <v>65.59527172763798</v>
       </c>
       <c r="U4">
-        <v>29.40178799801884</v>
+        <v>39.0331010994409</v>
       </c>
       <c r="V4">
-        <v>174.3930067069952</v>
+        <v>195.0747659498717</v>
       </c>
       <c r="W4">
-        <v>154.3325995392204</v>
+        <v>181.7019049196011</v>
       </c>
       <c r="Z4">
-        <v>1.632490666555805E-14</v>
+        <v>1.948425238244579E-14</v>
       </c>
       <c r="AA4">
-        <v>16.74074845574643</v>
+        <v>19.61055887531345</v>
       </c>
       <c r="AB4">
-        <v>14.31328984684339</v>
+        <v>15.12169004693073</v>
       </c>
       <c r="AC4">
-        <v>1.912177556460683E-16</v>
+        <v>-3.290819308807874E-17</v>
       </c>
       <c r="AD4">
-        <v>0.6588549136336986</v>
+        <v>0.7809675478866551</v>
       </c>
       <c r="AE4">
-        <v>5.209002350866882</v>
+        <v>0.2732647625291972</v>
       </c>
       <c r="AF4">
-        <v>21.66773013349517</v>
+        <v>27.29024809152821</v>
       </c>
       <c r="AG4">
-        <v>0.1329977263740609</v>
+        <v>0.1145514632476978</v>
       </c>
       <c r="AH4">
-        <v>1467.741144857041</v>
+        <v>1637.631278806614</v>
       </c>
       <c r="AJ4">
-        <v>31.67430216102505</v>
+        <v>34.06684321123263</v>
       </c>
       <c r="AK4">
-        <v>515.5558512826483</v>
+        <v>573.9121039858803</v>
       </c>
       <c r="AL4">
-        <v>111.6368892326615</v>
+        <v>111.3065775303098</v>
       </c>
       <c r="AM4">
-        <v>371.5033769081213</v>
+        <v>223.0083036835496</v>
       </c>
       <c r="AN4">
-        <v>23.85005407444833</v>
+        <v>23.78472302960183</v>
       </c>
       <c r="AO4">
-        <v>44.80826046455707</v>
+        <v>37.31255486423841</v>
       </c>
       <c r="AP4">
-        <v>638.5754174162465</v>
+        <v>706.1995342774608</v>
       </c>
       <c r="AQ4">
-        <v>98.51454690879596</v>
+        <v>110.2971352872312</v>
       </c>
       <c r="AR4">
-        <v>42.64297852264453</v>
+        <v>52.12223544712884</v>
       </c>
       <c r="AS4">
-        <v>6.297758391251802</v>
+        <v>8.090145085803432</v>
       </c>
       <c r="AT4">
-        <v>3.556457289773483</v>
+        <v>4.242347816781932</v>
       </c>
       <c r="AU4">
-        <v>62.06944792747284</v>
+        <v>68.13251346564036</v>
       </c>
       <c r="AV4">
         <v>1</v>
@@ -1020,133 +1020,133 @@
         </is>
       </c>
       <c r="B5">
-        <v>1301.932785527653</v>
+        <v>1460.592575578642</v>
       </c>
       <c r="C5">
-        <v>223.9449958347172</v>
+        <v>241.8073816732181</v>
       </c>
       <c r="D5">
-        <v>3230.766258960618</v>
+        <v>3469.706886853726</v>
       </c>
       <c r="E5">
-        <v>447.8141805690632</v>
+        <v>452.1427759327515</v>
       </c>
       <c r="F5">
-        <v>1183.732105723766</v>
+        <v>1328.377284248486</v>
       </c>
       <c r="G5">
-        <v>89.59484015419247</v>
+        <v>103.7451791734996</v>
       </c>
       <c r="H5">
-        <v>0.2295625819436307</v>
+        <v>0.4009881004747676</v>
       </c>
       <c r="I5">
-        <v>162.7526513266641</v>
+        <v>171.1220723086487</v>
       </c>
       <c r="J5">
-        <v>84.22655225130612</v>
+        <v>92.52883248870894</v>
       </c>
       <c r="K5">
-        <v>1.642141258830716E-15</v>
+        <v>-8.392233834593444E-15</v>
       </c>
       <c r="L5">
-        <v>1266.679397003511</v>
+        <v>1303.925568241643</v>
       </c>
       <c r="M5">
-        <v>1230.845232219592</v>
+        <v>1289.405236892077</v>
       </c>
       <c r="N5">
-        <v>715.3865320783368</v>
+        <v>760.3830029046389</v>
       </c>
       <c r="O5">
-        <v>184.4210615477502</v>
+        <v>233.7265606296236</v>
       </c>
       <c r="P5">
-        <v>14.45203567677946</v>
+        <v>14.08555680430675</v>
       </c>
       <c r="Q5">
-        <v>0.1301307593434843</v>
+        <v>0.06541793417151308</v>
       </c>
       <c r="R5">
-        <v>0.004352207223269753</v>
+        <v>0.265708805789203</v>
       </c>
       <c r="S5">
-        <v>134.1590615026118</v>
+        <v>117.1837238828853</v>
       </c>
       <c r="T5">
-        <v>316.1643435699443</v>
+        <v>339.6091028455801</v>
       </c>
       <c r="U5">
-        <v>96.28334579578093</v>
+        <v>99.30641144315895</v>
       </c>
       <c r="V5">
-        <v>488.6389946463161</v>
+        <v>551.3577001748788</v>
       </c>
       <c r="W5">
-        <v>234.3649186983873</v>
+        <v>256.6468473756426</v>
       </c>
       <c r="Z5">
-        <v>2.107871998061202E-15</v>
+        <v>4.911444812554091E-14</v>
       </c>
       <c r="AA5">
-        <v>33.91456515698325</v>
+        <v>37.48035786744583</v>
       </c>
       <c r="AB5">
-        <v>44.83189637958399</v>
+        <v>53.67553681231848</v>
       </c>
       <c r="AC5">
-        <v>-8.165313336110961E-16</v>
+        <v>-3.836732016616559E-15</v>
       </c>
       <c r="AD5">
-        <v>0.42555052960083</v>
+        <v>0.479649587854262</v>
       </c>
       <c r="AE5">
-        <v>0.09316482877756978</v>
+        <v>0.03698727818255388</v>
       </c>
       <c r="AF5">
-        <v>20.31031761193005</v>
+        <v>0.4705683846101806</v>
       </c>
       <c r="AG5">
-        <v>0.09979061298377558</v>
+        <v>0.08113681559864491</v>
       </c>
       <c r="AH5">
-        <v>536.2484760072468</v>
+        <v>585.3675910800976</v>
       </c>
       <c r="AJ5">
-        <v>15.70752503877175</v>
+        <v>17.27238157942843</v>
       </c>
       <c r="AK5">
-        <v>430.3855210300598</v>
+        <v>408.2204371982371</v>
       </c>
       <c r="AL5">
-        <v>73.6495993607746</v>
+        <v>72.17774757180905</v>
       </c>
       <c r="AM5">
-        <v>22.58977193419741</v>
+        <v>11.17298809827064</v>
       </c>
       <c r="AN5">
-        <v>9.648973950903997</v>
+        <v>9.915221752348918</v>
       </c>
       <c r="AO5">
-        <v>23.41437098884867</v>
+        <v>21.49006233628671</v>
       </c>
       <c r="AP5">
-        <v>772.80113433933</v>
+        <v>814.1778206104577</v>
       </c>
       <c r="AQ5">
-        <v>219.2005319339643</v>
+        <v>236.0031015995712</v>
       </c>
       <c r="AR5">
-        <v>66.88481025894131</v>
+        <v>53.0315445845952</v>
       </c>
       <c r="AS5">
-        <v>3.373029408646567</v>
+        <v>4.344693368475549</v>
       </c>
       <c r="AT5">
-        <v>3.104655097824373</v>
+        <v>2.526439990033837</v>
       </c>
       <c r="AU5">
-        <v>40.3179789405644</v>
+        <v>41.09426229608826</v>
       </c>
       <c r="AV5">
         <v>1</v>
@@ -1159,133 +1159,133 @@
         </is>
       </c>
       <c r="B6">
-        <v>445.9319608102741</v>
+        <v>523.6222290747421</v>
       </c>
       <c r="C6">
-        <v>78.27886416268849</v>
+        <v>84.36839850295289</v>
       </c>
       <c r="D6">
-        <v>6481.426244135848</v>
+        <v>7154.229862351052</v>
       </c>
       <c r="E6">
-        <v>198.1832109233268</v>
+        <v>256.471443954926</v>
       </c>
       <c r="F6">
-        <v>402.1799409882482</v>
+        <v>467.2377202102275</v>
       </c>
       <c r="G6">
-        <v>26.35809438470729</v>
+        <v>31.65709835856308</v>
       </c>
       <c r="H6">
-        <v>3.308690012970168</v>
+        <v>4.485234944788139</v>
       </c>
       <c r="I6">
-        <v>213.4584245973646</v>
+        <v>227.5981179885025</v>
       </c>
       <c r="J6">
-        <v>51.42057406330687</v>
+        <v>54.81680948687411</v>
       </c>
       <c r="K6">
-        <v>2.830234479193998E-15</v>
+        <v>7.146073431570305E-15</v>
       </c>
       <c r="L6">
-        <v>3775.11480058472</v>
+        <v>4194.763232427769</v>
       </c>
       <c r="M6">
-        <v>1601.900283185841</v>
+        <v>1754.655872245822</v>
       </c>
       <c r="N6">
-        <v>950.1406652551589</v>
+        <v>1014.167335362479</v>
       </c>
       <c r="O6">
-        <v>124.7384472413289</v>
+        <v>174.5055130731807</v>
       </c>
       <c r="P6">
-        <v>16.19710613349369</v>
+        <v>17.44562173331713</v>
       </c>
       <c r="Q6">
-        <v>2.350037609270177</v>
+        <v>2.999543751511336</v>
       </c>
       <c r="R6">
-        <v>6.422680679349327</v>
+        <v>9.454290137911215</v>
       </c>
       <c r="S6">
-        <v>19.4904761904756</v>
+        <v>22.82782238305218</v>
       </c>
       <c r="T6">
-        <v>34.18051474628494</v>
+        <v>40.19492581919095</v>
       </c>
       <c r="U6">
-        <v>42.11274395706574</v>
+        <v>49.26645631769541</v>
       </c>
       <c r="V6">
-        <v>134.308799914295</v>
+        <v>149.0587425950698</v>
       </c>
       <c r="W6">
-        <v>146.2596571789049</v>
+        <v>176.9724412206224</v>
       </c>
       <c r="Z6">
-        <v>1.338260970536094E-14</v>
+        <v>1.611285502847868E-14</v>
       </c>
       <c r="AA6">
-        <v>10.35181432325125</v>
+        <v>11.74109880289519</v>
       </c>
       <c r="AB6">
-        <v>16.3395336723304</v>
+        <v>19.06558734423207</v>
       </c>
       <c r="AC6">
-        <v>1.683314273131461E-16</v>
+        <v>-1.542635869397706E-17</v>
       </c>
       <c r="AD6">
-        <v>1.896342895799407</v>
+        <v>2.713943778512221</v>
       </c>
       <c r="AE6">
-        <v>3.116385250387523</v>
+        <v>6.370504097726922</v>
       </c>
       <c r="AF6">
-        <v>24.5147055645597</v>
+        <v>33.46588557345914</v>
       </c>
       <c r="AG6">
-        <v>0.3634059767714994</v>
+        <v>0.441501789781972</v>
       </c>
       <c r="AH6">
-        <v>2530.735674617337</v>
+        <v>2798.072175975</v>
       </c>
       <c r="AJ6">
-        <v>52.07491445427728</v>
+        <v>54.68343238668422</v>
       </c>
       <c r="AK6">
-        <v>542.976066324374</v>
+        <v>621.5323996649465</v>
       </c>
       <c r="AL6">
-        <v>109.6256099033816</v>
+        <v>106.5805140286088</v>
       </c>
       <c r="AM6">
-        <v>214.6332325581395</v>
+        <v>71.8504468738013</v>
       </c>
       <c r="AN6">
-        <v>36.673764832331</v>
+        <v>36.91147952663471</v>
       </c>
       <c r="AO6">
-        <v>67.85984163373516</v>
+        <v>59.22631701054202</v>
       </c>
       <c r="AP6">
-        <v>1153.518123212063</v>
+        <v>1267.501466195757</v>
       </c>
       <c r="AQ6">
-        <v>140.8569552956586</v>
+        <v>148.5381541341336</v>
       </c>
       <c r="AR6">
-        <v>75.83103065107619</v>
+        <v>90.43683677580486</v>
       </c>
       <c r="AS6">
-        <v>10.32303576391954</v>
+        <v>11.73249902229175</v>
       </c>
       <c r="AT6">
-        <v>3.768033926016759</v>
+        <v>3.924270139309509</v>
       </c>
       <c r="AU6">
-        <v>113.6042090784041</v>
+        <v>132.6223932825442</v>
       </c>
       <c r="AV6">
         <v>1</v>
@@ -1298,133 +1298,133 @@
         </is>
       </c>
       <c r="B7">
-        <v>837.5910439660321</v>
+        <v>891.3051680874439</v>
       </c>
       <c r="C7">
-        <v>193.8907923226405</v>
+        <v>197.5892987764462</v>
       </c>
       <c r="D7">
-        <v>4094.032462370825</v>
+        <v>4450.153661369418</v>
       </c>
       <c r="E7">
-        <v>273.9346762967269</v>
+        <v>347.1796050403274</v>
       </c>
       <c r="F7">
-        <v>736.3313570746276</v>
+        <v>800.0989158126064</v>
       </c>
       <c r="G7">
-        <v>63.69256290278772</v>
+        <v>71.04806706024998</v>
       </c>
       <c r="H7">
-        <v>0.7746208904722398</v>
+        <v>0.8305738952800974</v>
       </c>
       <c r="I7">
-        <v>175.9191045983209</v>
+        <v>180.6104466117005</v>
       </c>
       <c r="J7">
-        <v>75.63556320978961</v>
+        <v>81.04783096049411</v>
       </c>
       <c r="K7">
-        <v>8.926015206496947E-15</v>
+        <v>5.669201301803542E-15</v>
       </c>
       <c r="L7">
-        <v>2026.289852285764</v>
+        <v>2276.069101684627</v>
       </c>
       <c r="M7">
-        <v>1087.090359894396</v>
+        <v>1227.606295609595</v>
       </c>
       <c r="N7">
-        <v>828.2224755879521</v>
+        <v>898.3529341094752</v>
       </c>
       <c r="O7">
-        <v>106.2057836976067</v>
+        <v>158.7853247893488</v>
       </c>
       <c r="P7">
-        <v>17.17866495363943</v>
+        <v>20.77172192181084</v>
       </c>
       <c r="Q7">
-        <v>0.6270156087063974</v>
+        <v>0.3668596975139611</v>
       </c>
       <c r="R7">
-        <v>1.52712047585991</v>
+        <v>1.831159383074676</v>
       </c>
       <c r="S7">
-        <v>57.56796892889664</v>
+        <v>61.23853363207878</v>
       </c>
       <c r="T7">
-        <v>145.5025496688742</v>
+        <v>164.1651734524772</v>
       </c>
       <c r="U7">
-        <v>53.07735231367791</v>
+        <v>59.33497942798691</v>
       </c>
       <c r="V7">
-        <v>276.5980091994158</v>
+        <v>300.5457029092995</v>
       </c>
       <c r="W7">
-        <v>180.8731070353134</v>
+        <v>213.2982924035633</v>
       </c>
       <c r="Z7">
-        <v>1.65110551114328E-14</v>
+        <v>2.751550414712982E-14</v>
       </c>
       <c r="AA7">
-        <v>26.28170383515081</v>
+        <v>27.7801477589211</v>
       </c>
       <c r="AB7">
-        <v>27.36315398330906</v>
+        <v>35.09177031764311</v>
       </c>
       <c r="AC7">
-        <v>2.940390453779014E-16</v>
+        <v>8.749786991006244E-16</v>
       </c>
       <c r="AD7">
-        <v>0.5271790768097085</v>
+        <v>0.5743343049799817</v>
       </c>
       <c r="AE7">
-        <v>0.9333712496169002</v>
+        <v>0.2333747907199235</v>
       </c>
       <c r="AF7">
-        <v>44.19614922762778</v>
+        <v>9.785832410219761</v>
       </c>
       <c r="AG7">
-        <v>0.1943057058239</v>
+        <v>0.295735790808919</v>
       </c>
       <c r="AH7">
-        <v>1031.507438022308</v>
+        <v>1152.882486318862</v>
       </c>
       <c r="AJ7">
-        <v>23.62072518576234</v>
+        <v>25.20471970857072</v>
       </c>
       <c r="AK7">
-        <v>483.3765267265483</v>
+        <v>526.4172527315511</v>
       </c>
       <c r="AL7">
-        <v>96.149016488773</v>
+        <v>96.72900140160365</v>
       </c>
       <c r="AM7">
-        <v>222.2858084654976</v>
+        <v>66.85576903085574</v>
       </c>
       <c r="AN7">
-        <v>16.11258454756188</v>
+        <v>16.30211344074861</v>
       </c>
       <c r="AO7">
-        <v>28.55713207448603</v>
+        <v>22.9586533407364</v>
       </c>
       <c r="AP7">
-        <v>691.0153204700474</v>
+        <v>761.5284795760674</v>
       </c>
       <c r="AQ7">
-        <v>171.3600402128918</v>
+        <v>186.1282485827305</v>
       </c>
       <c r="AR7">
-        <v>51.67041123921508</v>
+        <v>61.28009885378517</v>
       </c>
       <c r="AS7">
-        <v>3.911639401428203</v>
+        <v>5.208827836977931</v>
       </c>
       <c r="AT7">
-        <v>2.396776360188834</v>
+        <v>2.213146826119016</v>
       </c>
       <c r="AU7">
-        <v>61.93697406181011</v>
+        <v>61.80525493251891</v>
       </c>
       <c r="AV7">
         <v>1</v>
@@ -1437,142 +1437,142 @@
         </is>
       </c>
       <c r="B8">
-        <v>1796.61152857726</v>
+        <v>1937.714833454398</v>
       </c>
       <c r="C8">
-        <v>265.8753857855442</v>
+        <v>289.386439318174</v>
       </c>
       <c r="D8">
-        <v>2876.921237293286</v>
+        <v>3059.122500496965</v>
       </c>
       <c r="E8">
-        <v>366.5021721526072</v>
+        <v>455.1798147897777</v>
       </c>
       <c r="F8">
-        <v>1753.010383187979</v>
+        <v>1784.80022896126</v>
       </c>
       <c r="G8">
-        <v>117.9832301768235</v>
+        <v>127.1883232622708</v>
       </c>
       <c r="H8">
-        <v>0.1546183467924729</v>
+        <v>0.1331802736722345</v>
       </c>
       <c r="I8">
-        <v>182.8940122449992</v>
+        <v>183.4049496672048</v>
       </c>
       <c r="J8">
-        <v>92.70566716021733</v>
+        <v>97.84115116198208</v>
       </c>
       <c r="K8">
-        <v>1.145016330378179E-14</v>
+        <v>9.86193282965853E-15</v>
       </c>
       <c r="L8">
-        <v>1209.712255570433</v>
+        <v>1203.185364131593</v>
       </c>
       <c r="M8">
-        <v>1043.734268449122</v>
+        <v>1100.323084496504</v>
       </c>
       <c r="N8">
-        <v>558.1106609068278</v>
+        <v>592.2371447248622</v>
       </c>
       <c r="O8">
-        <v>183.1107005307805</v>
+        <v>212.0752048817686</v>
       </c>
       <c r="P8">
-        <v>15.4785666475579</v>
+        <v>15.12467149100788</v>
       </c>
       <c r="Q8">
-        <v>0.005116388842846801</v>
+        <v>0.002983257760006936</v>
       </c>
       <c r="R8">
-        <v>0.4988188818427156</v>
+        <v>0.4500406805860108</v>
       </c>
       <c r="S8">
-        <v>135.3360779869306</v>
+        <v>156.9693812679122</v>
       </c>
       <c r="T8">
-        <v>454.3038371661468</v>
+        <v>486.2773444762719</v>
       </c>
       <c r="U8">
-        <v>131.1992027024653</v>
+        <v>141.7821484109462</v>
       </c>
       <c r="V8">
-        <v>771.7633705909843</v>
+        <v>852.5636359467562</v>
       </c>
       <c r="W8">
-        <v>285.6048532136859</v>
+        <v>289.0105702168734</v>
       </c>
       <c r="X8">
-        <v>3928.699041553994</v>
+        <v>4203.961932344067</v>
       </c>
       <c r="Y8">
-        <v>619.6702869300105</v>
+        <v>660.8749918098674</v>
       </c>
       <c r="Z8">
-        <v>5.765211532605332E-14</v>
+        <v>4.572886185082399E-14</v>
       </c>
       <c r="AA8">
-        <v>42.53323806684065</v>
+        <v>46.38257112385004</v>
       </c>
       <c r="AB8">
-        <v>72.45322182696476</v>
+        <v>78.7599574803541</v>
       </c>
       <c r="AC8">
-        <v>3.184865358485513E-15</v>
+        <v>-4.042668915548677E-15</v>
       </c>
       <c r="AD8">
-        <v>0.2151432096491942</v>
+        <v>0.1398656778453049</v>
       </c>
       <c r="AE8">
-        <v>0.04635095690185447</v>
+        <v>0.04901506045664716</v>
       </c>
       <c r="AF8">
-        <v>0.0009456479956068093</v>
+        <v>0.006598418072300684</v>
       </c>
       <c r="AG8">
-        <v>0.2607122310393321</v>
+        <v>0.1857311541027352</v>
       </c>
       <c r="AH8">
-        <v>285.6701821945007</v>
+        <v>312.0072662537014</v>
       </c>
       <c r="AI8">
-        <v>429.4473048975834</v>
+        <v>467.5037520550409</v>
       </c>
       <c r="AJ8">
-        <v>13.7594554768997</v>
+        <v>14.99007651192478</v>
       </c>
       <c r="AK8">
-        <v>469.3152762627372</v>
+        <v>548.450142601779</v>
       </c>
       <c r="AL8">
-        <v>56.131762108763</v>
+        <v>57.12413272569263</v>
       </c>
       <c r="AM8">
-        <v>22.02199208770624</v>
+        <v>8.54121400043887</v>
       </c>
       <c r="AN8">
-        <v>9.831075846547616</v>
+        <v>10.40237820184053</v>
       </c>
       <c r="AO8">
-        <v>14.09370786422572</v>
+        <v>14.11952875600906</v>
       </c>
       <c r="AP8">
-        <v>593.1679324330312</v>
+        <v>651.444910933334</v>
       </c>
       <c r="AQ8">
-        <v>198.7949708029965</v>
+        <v>218.0144169417276</v>
       </c>
       <c r="AR8">
-        <v>69.93276090379108</v>
+        <v>69.91693512193434</v>
       </c>
       <c r="AS8">
-        <v>2.622626479642321</v>
+        <v>3.294770475866244</v>
       </c>
       <c r="AT8">
-        <v>3.344997150502261</v>
+        <v>2.860511024140645</v>
       </c>
       <c r="AU8">
-        <v>19.66746701761627</v>
+        <v>17.56023506505824</v>
       </c>
       <c r="AV8">
         <v>1</v>
@@ -1585,133 +1585,133 @@
         </is>
       </c>
       <c r="B9">
-        <v>561.1711120970127</v>
+        <v>657.2683527566114</v>
       </c>
       <c r="C9">
-        <v>80.17546451398516</v>
+        <v>85.14539029535865</v>
       </c>
       <c r="D9">
-        <v>10169.97456161715</v>
+        <v>11201.99267112598</v>
       </c>
       <c r="E9">
-        <v>311.166354556804</v>
+        <v>404.1195760715968</v>
       </c>
       <c r="F9">
-        <v>513.4506457242583</v>
+        <v>606.4035453047776</v>
       </c>
       <c r="G9">
-        <v>28.25277403035413</v>
+        <v>30.25506168158294</v>
       </c>
       <c r="H9">
-        <v>9.429919490622922</v>
+        <v>7.630503610722181</v>
       </c>
       <c r="I9">
-        <v>314.4276743979578</v>
+        <v>340.7338285548798</v>
       </c>
       <c r="J9">
-        <v>50.05929058995612</v>
+        <v>55.70274542429285</v>
       </c>
       <c r="K9">
-        <v>8.751111986347475E-15</v>
+        <v>5.520453425025361E-15</v>
       </c>
       <c r="L9">
-        <v>6491.547475685321</v>
+        <v>7187.304139642621</v>
       </c>
       <c r="M9">
-        <v>2435.420537822475</v>
+        <v>2781.964730384243</v>
       </c>
       <c r="N9">
-        <v>987.0711127049324</v>
+        <v>1060.743629523467</v>
       </c>
       <c r="O9">
-        <v>217.5751097602895</v>
+        <v>298.394415274463</v>
       </c>
       <c r="P9">
-        <v>30.88367524302601</v>
+        <v>39.49272680010397</v>
       </c>
       <c r="Q9">
-        <v>6.939314159292035</v>
+        <v>9.573709821428572</v>
       </c>
       <c r="R9">
-        <v>4.605631720430107</v>
+        <v>3.204485111071812</v>
       </c>
       <c r="S9">
-        <v>27.9665899677841</v>
+        <v>29.35287661231341</v>
       </c>
       <c r="T9">
-        <v>38.99635266660223</v>
+        <v>46.03375039389823</v>
       </c>
       <c r="U9">
-        <v>57.9609125833565</v>
+        <v>67.3756381660471</v>
       </c>
       <c r="V9">
-        <v>136.674523988006</v>
+        <v>146.82375</v>
       </c>
       <c r="W9">
-        <v>212.8918471262052</v>
+        <v>260.3667923151751</v>
       </c>
       <c r="Z9">
-        <v>1.656450225198276E-14</v>
+        <v>2.340006468883112E-14</v>
       </c>
       <c r="AA9">
-        <v>9.393593074804929</v>
+        <v>10.70982877860762</v>
       </c>
       <c r="AB9">
-        <v>17.53706547109176</v>
+        <v>19.71559536360483</v>
       </c>
       <c r="AC9">
-        <v>-6.550667687791186E-17</v>
+        <v>7.587348998258752E-17</v>
       </c>
       <c r="AD9">
-        <v>5.904853987079436</v>
+        <v>5.760660571428572</v>
       </c>
       <c r="AE9">
-        <v>0.8828006757380926</v>
+        <v>2.216957599118943</v>
       </c>
       <c r="AF9">
-        <v>28.41241329883929</v>
+        <v>22.81065088757396</v>
       </c>
       <c r="AG9">
-        <v>1.166276791181874</v>
+        <v>0.5362524525833878</v>
       </c>
       <c r="AH9">
-        <v>5097.603213399504</v>
+        <v>5653.549132719421</v>
       </c>
       <c r="AJ9">
-        <v>105.5688230062259</v>
+        <v>111.3280144524274</v>
       </c>
       <c r="AK9">
-        <v>601.4485250737464</v>
+        <v>664.5288316272503</v>
       </c>
       <c r="AL9">
-        <v>112.4011973525872</v>
+        <v>105.2837213986881</v>
       </c>
       <c r="AM9">
-        <v>26.81096291476903</v>
+        <v>49.67909836065574</v>
       </c>
       <c r="AN9">
-        <v>52.58240262476389</v>
+        <v>58.06531453843269</v>
       </c>
       <c r="AO9">
-        <v>115.1446344530825</v>
+        <v>104.6646471054731</v>
       </c>
       <c r="AP9">
-        <v>1882.956319710086</v>
+        <v>2061.439374649308</v>
       </c>
       <c r="AQ9">
-        <v>152.5197269615932</v>
+        <v>160.8551168139742</v>
       </c>
       <c r="AR9">
-        <v>110.6665533882534</v>
+        <v>141.6772164009112</v>
       </c>
       <c r="AS9">
-        <v>17.51364640883978</v>
+        <v>20.86247018610833</v>
       </c>
       <c r="AT9">
-        <v>5.60659090909091</v>
+        <v>4.672601164551887</v>
       </c>
       <c r="AU9">
-        <v>190.377772173541</v>
+        <v>209.7273151848152</v>
       </c>
       <c r="AV9">
         <v>1</v>
